--- a/base_datos_fondos_clasificada_con_liquidativos.xlsx
+++ b/base_datos_fondos_clasificada_con_liquidativos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidarduramoyano/app_carteras/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidarduramoyano/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04649210-9D9D-8544-9644-2C86E2782DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9A6EB6-A6D9-7547-B19E-24F371374291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="20300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="780" windowWidth="29900" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clasificación fondos" sheetId="1" r:id="rId1"/>
@@ -1362,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1420,7 +1420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15">
+    <row r="2" spans="1:14" ht="16">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
@@ -1464,7 +1464,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15">
+    <row r="3" spans="1:14" ht="16">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>27</v>
@@ -1508,7 +1508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15">
+    <row r="4" spans="1:14" ht="16">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15">
+    <row r="5" spans="1:14" ht="16">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15">
+    <row r="6" spans="1:14" ht="16">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15">
+    <row r="7" spans="1:14" ht="16">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15">
+    <row r="8" spans="1:14" ht="16">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -1728,7 +1728,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15">
+    <row r="9" spans="1:14" ht="16">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>48</v>
@@ -1772,7 +1772,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15">
+    <row r="10" spans="1:14" ht="16">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15">
+    <row r="11" spans="1:14" ht="16">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" ht="16">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15">
+    <row r="13" spans="1:14" ht="16">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15">
+    <row r="14" spans="1:14" ht="16">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -1992,7 +1992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15">
+    <row r="15" spans="1:14" ht="16">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15">
+    <row r="16" spans="1:14" ht="16">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15">
+    <row r="17" spans="1:14" ht="16">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15">
+    <row r="18" spans="1:14" ht="16">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15">
+    <row r="19" spans="1:14" ht="16">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15">
+    <row r="20" spans="1:14" ht="16">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15">
+    <row r="21" spans="1:14" ht="16">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15">
+    <row r="22" spans="1:14" ht="16">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15">
+    <row r="23" spans="1:14" ht="16">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15">
+    <row r="24" spans="1:14" ht="16">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15">
+    <row r="25" spans="1:14" ht="16">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15">
+    <row r="26" spans="1:14" ht="16">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>16</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>125</v>
@@ -2520,7 +2520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15">
+    <row r="27" spans="1:14" ht="16">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15">
+    <row r="28" spans="1:14" ht="16">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15">
+    <row r="29" spans="1:14" ht="16">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15">
+    <row r="30" spans="1:14" ht="16">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15">
+    <row r="31" spans="1:14" ht="16">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15">
+    <row r="32" spans="1:14" ht="16">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>155</v>
@@ -2784,7 +2784,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15">
+    <row r="33" spans="1:14" ht="16">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15">
+    <row r="34" spans="1:14" ht="16">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15">
+    <row r="35" spans="1:14" ht="16">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15">
+    <row r="36" spans="1:14" ht="16">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15">
+    <row r="37" spans="1:14" ht="16">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15">
+    <row r="38" spans="1:14" ht="16">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15">
+    <row r="39" spans="1:14" ht="16">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15">
+    <row r="40" spans="1:14" ht="16">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15">
+    <row r="41" spans="1:14" ht="16">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15">
+    <row r="42" spans="1:14" ht="16">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15">
+    <row r="43" spans="1:14" ht="16">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15">
+    <row r="44" spans="1:14" ht="16">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15">
+    <row r="45" spans="1:14" ht="16">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15">
+    <row r="46" spans="1:14" ht="16">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15">
+    <row r="47" spans="1:14" ht="16">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15">
+    <row r="48" spans="1:14" ht="16">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15">
+    <row r="49" spans="1:14" ht="16">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15">
+    <row r="50" spans="1:14" ht="16">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15">
+    <row r="51" spans="1:14" ht="16">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15">
+    <row r="52" spans="1:14" ht="16">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15">
+    <row r="53" spans="1:14" ht="16">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15">
+    <row r="54" spans="1:14" ht="16">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="15">
+    <row r="55" spans="1:14" ht="16">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15">
+    <row r="56" spans="1:14" ht="16">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15">
+    <row r="57" spans="1:14" ht="16">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15">
+    <row r="58" spans="1:14" ht="16">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15">
+    <row r="59" spans="1:14" ht="16">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15">
+    <row r="60" spans="1:14" ht="16">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15">
+    <row r="61" spans="1:14" ht="16">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15">
+    <row r="62" spans="1:14" ht="16">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15">
+    <row r="63" spans="1:14" ht="16">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -4159,7 +4159,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4179,7 +4179,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15">
+    <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -4678,7 +4678,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="28" customWidth="1"/>
   </cols>
@@ -4690,7 +4690,7 @@
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
-    <row r="2" spans="1:3" ht="60">
+    <row r="2" spans="1:3" ht="64">
       <c r="A2" s="2" t="s">
         <v>300</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45">
+    <row r="3" spans="1:3" ht="48">
       <c r="A3" s="2" t="s">
         <v>303</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45">
+    <row r="4" spans="1:3" ht="48">
       <c r="A4" s="2" t="s">
         <v>306</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45">
+    <row r="5" spans="1:3" ht="64">
       <c r="A5" s="2" t="s">
         <v>308</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="60">
+    <row r="6" spans="1:3" ht="64">
       <c r="A6" s="2" t="s">
         <v>310</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15">
+    <row r="8" spans="1:3">
       <c r="A8" s="9" t="s">
         <v>313</v>
       </c>
@@ -4811,7 +4811,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BK65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="63" width="18" customWidth="1"/>
@@ -17240,7 +17240,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BK64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="63" width="18" customWidth="1"/>
@@ -33198,7 +33198,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
